--- a/Result/checksun_type/鋼胚.xlsx
+++ b/Result/checksun_type/鋼胚.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>31.65</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.62</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.35</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.35</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>88619.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>56397.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>56397</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>81909.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>71062.74</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>71062.74000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-6411.908493448966</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>88619</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>88619.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.41</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.66</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>34.41</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>34.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>30296.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>55604.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>55604.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>81238.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>75154.3</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>75154.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9133.301158309303</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>30296</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>30296.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.37</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.78</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>34.54</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>34.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>51673.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>67354.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>67354.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>87056.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>76625.64</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>76625.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-6445.922781027301</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>51673</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>51673.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.34</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.94</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>34.65</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>34.65</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>47092.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>74374.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>74374.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>92061.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>76543.48</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>76543.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-4666.992142730625</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>47092</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>47092.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.32</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.13</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>34.77</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>64305.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>91626.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>91626</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>98215.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>76798.64</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>76798.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1468.16294006641</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>64305</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>64305.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>31.49</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.35</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>34.89</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>34.89</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>84657.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>107421.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>107421.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>104305.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>77733.42</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>77733.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1309.777454456271</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>84657</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>84657.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>31.89</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.58</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>35.03</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>35.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>89047.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>106873.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>106873</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>107795.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>80213.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>80213.17999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>3050.914537543809</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>89047</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>89047.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.83</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>35.15</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.83</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>35.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>86773.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>106758.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>106758.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>107839.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>79632.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>79632.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>4958.934851327998</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>86773</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>86773.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>32.75</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>34.07</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>35.27</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>35.27</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>133348.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>109748.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>109748</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>110112.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>80021.1</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>80021.10000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>7751.216197757982</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>133348</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>133348.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.23</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>35.38</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>35.38</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>143284.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>104805.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>104805.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>105668.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>79834.04</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>79834.03999999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>6473.181828452303</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>143284</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>143284.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>33.52</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>34.47</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>35.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>81913.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>101188.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>101188.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>97048.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>81169.24</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>81169.24000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>3351.661949856643</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>81913</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>81913.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>15.57</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>16.25</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>16.25</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>3184280.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1257083.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1257083.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1064711.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1194971.18</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1194971.18</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>115356.4962169959</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>3184280</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>3184280.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>15.59</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>16.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>531740.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>700896.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>700896.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>833401.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1151490.38</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1151490.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-72499.9008129671</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>531740</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>531740.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>15.62</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>16.32</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16.32</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>833554.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>814799.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>814799.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>835888.7</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1161385.88</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1161385.88</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-54076.18582673674</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>833554</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>833554.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>16.37</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>16.37</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1131868.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>785167.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>785167.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>813053.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1159266.78</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1159266.78</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-58162.51492402435</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1131868</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1131868.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>15.59</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>15.72</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16.42</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>603975.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>738452.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>738452.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>763557.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1150552.12</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1150552.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-93885.1095300056</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>603975</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>603975.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>15.77</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>16.46</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>16.46</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>403346.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>872339.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>872339.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>836711.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1144166.26</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1144166.26</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-85004.38362676429</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>403346</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>403346.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>15.73</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>15.81</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>16.51</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1101255.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>965907.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>965907</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1038595.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1149632.4</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1149632.4</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-47785.7972068924</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1101255</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1101255.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>15.69</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>15.85</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>16.55</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>685393.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>856977.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>856977.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>989811.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1135853.02</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1135853.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-67685.71670682915</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>685393</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>685393.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>15.7</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>15.9</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>16.6</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>898294.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>840940.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>840940.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1123941.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1153041.94</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1153041.94</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-49140.18325292331</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>898294</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>898294.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>15.68</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>15.92</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>16.64</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>16.64</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1273408.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>788661.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>788661.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1184457.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1162483.82</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1162483.82</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-43702.37891688233</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1273408</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1273408.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>15.63</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>15.94</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>16.68</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>16.68</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>871185.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>801084.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>801084</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1164826.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1166986.14</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1166986.14</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-74564.07347550616</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>871185</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>871185.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>62.32000000000001</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>62.9</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>63.97</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>63.97</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>8704280.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>15719796.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>15719796.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>16939283.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>13673755.8</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>13673755.8</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>300733.1929959357</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>8704280</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>8704280.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>62.0</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>62.98</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>64.01</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>64.01000000000001</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>13613590.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>17803283.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>17803283</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>16874989.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>13822222.76</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>13822222.76</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>1103502.94642511</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>13613590</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>13613590.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>61.77999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>63.07</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>64.07</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>64.06999999999999</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>28665421.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>23370009.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>23370009.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>16069191.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>13761553.84</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>13761553.84</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>1684908.560380183</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>28665421</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>28665421.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>61.77999999999999</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>63.17</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>64.11</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>64.11</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>16299112.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>20389573.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>20389573.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>13844080.7</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>13405829.02</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>13405829.02</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>842616.524588136</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>16299112</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>16299112.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>62.17999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>63.25</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>64.17</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>11316581.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>19068893.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>19068893.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>13318414.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>13267845.18</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>13267845.18</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>934210.419007061</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>11316581</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>11316581.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>62.64</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>63.39</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>64.25</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>64.25</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>19121711.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>18158769.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>18158769.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>13467231.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>13228258.1</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>13228258.1</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>1565536.788926702</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>19121711</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>19121711.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>63.27999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>64.35</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>64.34999999999999</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>41447222.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>15946696.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>15946696.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>12569121.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>12937127.38</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>12937127.38</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>1575255.646350237</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>41447222</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>41447222.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>63.67999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>63.63</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>64.42</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>64.42</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>13763241.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>8768373.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>8768373</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>10303528.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>12259767.7</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>12259767.7</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-859138.4375572242</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>13763241</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>13763241.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>63.85999999999999</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>63.69</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>64.46</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>64.45999999999999</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>9695711.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>7298588.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>7298588</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>10025901.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>12286433.32</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>12286433.32</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-1340019.934655124</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>9695711</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>9695711.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>63.8</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>63.72</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>64.49</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>64.48999999999999</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>6765962.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>7567936.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>7567936.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>10961368.5</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>12385281.66</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>12385281.66</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-1543328.86141444</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>6765962</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>6765962.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>63.8</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>63.93</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>64.55</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>64.55</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>8061347.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>8775693.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>8775693.800000001</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>11351024.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>12459611.04</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>12459611.04</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-1464749.618877232</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>8061347</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>8061347.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>17.88</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>18.08</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>18.7</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>554883691.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>592834457.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>592834457.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>564016344.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>472987580.06</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>472987580.06</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>25737807.48307288</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>554883691</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>554883691.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>17.79</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>18.11</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>18.72</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>421676243.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>575373921.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>575373921</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>551015361.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>476205258.64</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>476205258.64</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>30387017.07643664</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>421676243</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>421676243.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>17.78</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>18.17</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>18.76</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>18.76</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1065633753.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>598121428.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>598121428.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>546982182.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>478593233.36</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>478593233.36</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>50215721.02851224</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1065633753</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1065633753.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>17.76</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>18.22</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>18.78</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>18.78</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>536795375.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>503700111.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>503700111.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>483479858.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>467113671.08</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>467113671.08</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>7753574.851887524</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>536795375</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>536795375.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>17.83</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>18.82</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>18.82</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>385183224.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>503682309.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>503682309</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>465278163.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>465379679.6</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>465379679.6</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>3477707.42628485</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>385183224</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>385183224.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>17.89</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>18.33</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>18.86</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>467581010.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>535198232.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>535198232.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>470575950.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>471154088.28</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>471154088.28</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>13489280.58877087</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>467581010</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>467581010.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>17.98</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>18.9</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>535413781.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>526656802.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>526656802.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>479649025.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>491243503.42</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>491243503.42</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>18481433.7284376</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>535413781</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>535413781.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>18.06</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>18.44</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>18.94</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>18.94</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>593527166.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>495842935.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>495842935.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>491705728.4</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>497565983.76</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>497565983.76</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>17685232.97337449</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>593527166</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>593527166.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>18.1</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>18.98</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>18.98</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>536706364.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>463259606.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>463259606.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>488073283.7</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>492693666.56</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>492693666.56</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>9689753.752806664</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>536706364</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>536706364.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>18.14</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>18.54</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>19.02</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>542762840.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>426874017.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>426874017.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>478988131.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>492160264.26</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>492160264.26</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>4009521.017966688</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>542762840</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>542762840.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>18.18</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>19.06</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>424873861.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>405953669.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>405953669</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>456595423.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>492268791.98</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>492268791.98</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-4897202.496732056</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>424873861</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>424873861.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
